--- a/14_extratask/01_Attendance/業務フロー（改善後）.xlsx
+++ b/14_extratask/01_Attendance/業務フロー（改善後）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f-otsuka\Desktop\workspace\14_extratask\01_Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7050E7D-E74C-4FED-9D89-5BB61897CAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482DA49E-078B-4649-8C69-FDA2C6CFE6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{103BD059-A4FD-4794-990E-CA928A745A99}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>従業員は出勤時カードリーダーにICカードをタッチ</t>
     <rPh sb="0" eb="3">
@@ -64,13 +64,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>残業申請</t>
-    <rPh sb="0" eb="4">
-      <t>ザンギョウシンセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>上長へ承認依頼通知</t>
     <rPh sb="0" eb="2">
       <t>ジョウチョウ</t>
@@ -127,12 +120,88 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>人事部によるデータ集計</t>
+    <t>はい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　　いいえ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人事部によって勤怠データの確定</t>
     <rPh sb="0" eb="3">
       <t>ジンジブ</t>
     </rPh>
+    <rPh sb="7" eb="9">
+      <t>キンタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員による残業申請</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ザンギョウシンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自動でデータ集計</t>
+    <rPh sb="0" eb="2">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　　承認</t>
+    <rPh sb="3" eb="5">
+      <t>ショウニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勤怠申請</t>
+    <rPh sb="0" eb="4">
+      <t>キンタイシンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マイページにて勤怠時間の
+確認／修正／削除</t>
+    <rPh sb="7" eb="9">
+      <t>キンタイ</t>
+    </rPh>
     <rPh sb="9" eb="11">
-      <t>シュウケイ</t>
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+差し戻し</t>
+    <rPh sb="1" eb="2">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -202,7 +271,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -217,6 +286,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -320,13 +395,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>2166257</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>468086</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -502,13 +577,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1110343</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>21772</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1115784</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>54428</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -555,13 +630,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1132115</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>489858</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1137556</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>21771</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -608,13 +683,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>32656</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>380999</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -694,13 +769,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1796142</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>381000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>43543</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>402771</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -747,13 +822,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>947058</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>952499</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>32656</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -800,13 +875,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>957944</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>963385</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>87085</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -853,13 +928,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>261258</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>283029</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -906,13 +981,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1132114</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>359229</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1132114</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>97972</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -959,13 +1034,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1132114</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>32657</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1137555</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>65313</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1012,13 +1087,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1132114</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1137555</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>32656</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1065,13 +1140,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1132114</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>10886</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1137555</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>43542</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1089,6 +1164,318 @@
         <a:xfrm>
           <a:off x="2710543" y="8860972"/>
           <a:ext cx="5441" cy="533399"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1143000</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>21772</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1148441</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="直線矢印コネクタ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03037DD0-0E2A-48D0-BDD9-202DD5C2D3EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2721429" y="7870372"/>
+          <a:ext cx="5441" cy="533399"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1110343</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1115784</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>32656</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="直線矢印コネクタ 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4442CAB-C1CF-4EA0-B164-D1249FA31E9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2721429" y="2841171"/>
+          <a:ext cx="5441" cy="533399"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1099457</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>10886</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1104898</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>43542</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線矢印コネクタ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CEB6C0A-CA29-4B08-B42E-3F581388A100}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2710543" y="3853543"/>
+          <a:ext cx="5441" cy="533399"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>239486</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1600200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>250371</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="直線コネクタ 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F21790CB-4A1F-1D80-CDD4-ACF76A131FAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="239486" y="8577943"/>
+          <a:ext cx="1360714" cy="21771"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>315686</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>261257</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="直線コネクタ 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE411272-6F86-F9B0-2222-02069183B826}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="228600" y="3657600"/>
+          <a:ext cx="0" cy="4953000"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>315686</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1589314</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>315686</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="35" name="直線矢印コネクタ 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20B7F6E5-6F55-03FC-BEC7-5658E1F0AA9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="3657600"/>
+          <a:ext cx="1360714" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1434,19 +1821,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF92B7A-A7DF-4DB3-B423-EBE23E245B3B}">
-  <dimension ref="A1:E38"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.69921875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="18.09765625" style="2" customWidth="1"/>
     <col min="2" max="2" width="28.5" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.69921875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="24.59765625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.69921875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.8984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.796875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.796875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="1" spans="2:4" ht="11.4" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="3" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="4" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
@@ -1460,73 +1850,109 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="7" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="6"/>
+    </row>
     <row r="8" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="4" t="s">
-        <v>3</v>
+      <c r="B8" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="9" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="6"/>
+    </row>
     <row r="10" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D10" s="4" t="s">
-        <v>2</v>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="11" spans="2:4" ht="39.6" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="12" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D12" s="4" t="s">
-        <v>3</v>
+      <c r="B12" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="14" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="4" t="s">
-        <v>5</v>
+      <c r="C14" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="16" spans="2:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="4" t="s">
+      <c r="D16" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="18" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="22" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="24" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="26" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="20" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="22" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="23" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="24" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="25" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="26" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="27" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="28" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="29" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="30" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="31" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="32" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="27" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="28" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="29" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="30" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="31" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="32" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="33" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="34" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="35" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="36" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="37" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="38" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="39" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="40" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="41" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="42" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="44" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>